--- a/proliferation_growth_curves/Incucyte_sheets/r2.xlsx
+++ b/proliferation_growth_curves/Incucyte_sheets/r2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/allielas/HTP_fibroblasts_mitolyso/proliferation_growth_curves/Incucyte_sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F09A544F-0DE6-A74A-8125-71DD19E23EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D6DCA4-C441-3342-BD98-41601E410AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-32660" yWindow="-340" windowWidth="27240" windowHeight="16260" xr2:uid="{4C1ABB4F-9716-DF4B-907D-36AFAFFFBF05}"/>
   </bookViews>
@@ -576,60 +576,6 @@
     <t>P15 LIN4-0B-b2 (B4), Image 9</t>
   </si>
   <si>
-    <t>P13 LIN5-0B-b3 LIN3-0A-b2 (A3), Image 1</t>
-  </si>
-  <si>
-    <t>P13 LIN5-0B-b3 LIN3-0A-b2 (A3), Image 2</t>
-  </si>
-  <si>
-    <t>P13 LIN5-0B-b3 LIN3-0A-b2 (A3), Image 3</t>
-  </si>
-  <si>
-    <t>P13 LIN5-0B-b3 LIN3-0A-b2 (A3), Image 4</t>
-  </si>
-  <si>
-    <t>P13 LIN5-0B-b3 LIN3-0A-b2 (A3), Image 5</t>
-  </si>
-  <si>
-    <t>P13 LIN5-0B-b3 LIN3-0A-b2 (A3), Image 6</t>
-  </si>
-  <si>
-    <t>P13 LIN5-0B-b3 LIN3-0A-b2 (A3), Image 7</t>
-  </si>
-  <si>
-    <t>P13 LIN5-0B-b3 LIN3-0A-b2 (A3), Image 8</t>
-  </si>
-  <si>
-    <t>P13 LIN5-0B-b3 LIN3-0A-b2 (A3), Image 9</t>
-  </si>
-  <si>
-    <t>P13 LIN5-0B-b3 LIN3-0A-b2 (B3), Image 1</t>
-  </si>
-  <si>
-    <t>P13 LIN5-0B-b3 LIN3-0A-b2 (B3), Image 2</t>
-  </si>
-  <si>
-    <t>P13 LIN5-0B-b3 LIN3-0A-b2 (B3), Image 3</t>
-  </si>
-  <si>
-    <t>P13 LIN5-0B-b3 LIN3-0A-b2 (B3), Image 4</t>
-  </si>
-  <si>
-    <t>P13 LIN5-0B-b3 LIN3-0A-b2 (B3), Image 5</t>
-  </si>
-  <si>
-    <t>P13 LIN5-0B-b3 LIN3-0A-b2 (B3), Image 6</t>
-  </si>
-  <si>
-    <t>P13 LIN5-0B-b3 LIN3-0A-b2 (B3), Image 7</t>
-  </si>
-  <si>
-    <t>P13 LIN5-0B-b3 LIN3-0A-b2 (B3), Image 8</t>
-  </si>
-  <si>
-    <t>P13 LIN5-0B-b3 LIN3-0A-b2 (B3), Image 9</t>
-  </si>
-  <si>
     <t>P11 LIN6-0C-b1 (C1), Image 1</t>
   </si>
   <si>
@@ -736,6 +682,60 @@
   </si>
   <si>
     <t>P13 LIN5-0B-b3 (C4), Image 9</t>
+  </si>
+  <si>
+    <t>P17 LIN3-0A-b2 (A3), Image 1</t>
+  </si>
+  <si>
+    <t>P17 LIN3-0A-b2 (A3), Image 2</t>
+  </si>
+  <si>
+    <t>P17 LIN3-0A-b2 (A3), Image 3</t>
+  </si>
+  <si>
+    <t>P17 LIN3-0A-b2 (A3), Image 4</t>
+  </si>
+  <si>
+    <t>P17 LIN3-0A-b2 (A3), Image 5</t>
+  </si>
+  <si>
+    <t>P17 LIN3-0A-b2 (A3), Image 6</t>
+  </si>
+  <si>
+    <t>P17 LIN3-0A-b2 (A3), Image 7</t>
+  </si>
+  <si>
+    <t>P17 LIN3-0A-b2 (A3), Image 8</t>
+  </si>
+  <si>
+    <t>P17 LIN3-0A-b2 (A3), Image 9</t>
+  </si>
+  <si>
+    <t>P17 LIN3-0A-b2 (B3), Image 1</t>
+  </si>
+  <si>
+    <t>P17 LIN3-0A-b2 (B3), Image 2</t>
+  </si>
+  <si>
+    <t>P17 LIN3-0A-b2 (B3), Image 3</t>
+  </si>
+  <si>
+    <t>P17 LIN3-0A-b2 (B3), Image 4</t>
+  </si>
+  <si>
+    <t>P17 LIN3-0A-b2 (B3), Image 5</t>
+  </si>
+  <si>
+    <t>P17 LIN3-0A-b2 (B3), Image 6</t>
+  </si>
+  <si>
+    <t>P17 LIN3-0A-b2 (B3), Image 7</t>
+  </si>
+  <si>
+    <t>P17 LIN3-0A-b2 (B3), Image 8</t>
+  </si>
+  <si>
+    <t>P17 LIN3-0A-b2 (B3), Image 9</t>
   </si>
 </sst>
 </file>
@@ -1750,58 +1750,58 @@
         <v>161</v>
       </c>
       <c r="AN1" s="4" t="s">
-        <v>180</v>
+        <v>216</v>
       </c>
       <c r="AO1" s="4" t="s">
-        <v>181</v>
+        <v>217</v>
       </c>
       <c r="AP1" s="4" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="AQ1" s="4" t="s">
-        <v>183</v>
+        <v>219</v>
       </c>
       <c r="AR1" s="4" t="s">
-        <v>184</v>
+        <v>220</v>
       </c>
       <c r="AS1" s="4" t="s">
-        <v>185</v>
+        <v>221</v>
       </c>
       <c r="AT1" s="4" t="s">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="AU1" s="4" t="s">
-        <v>187</v>
+        <v>223</v>
       </c>
       <c r="AV1" s="4" t="s">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="AW1" s="4" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="AX1" s="4" t="s">
-        <v>190</v>
+        <v>226</v>
       </c>
       <c r="AY1" s="4" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="AZ1" s="4" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="BA1" s="4" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="BB1" s="4" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="BC1" s="4" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="BD1" s="4" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="BE1" s="4" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="BF1" s="4" t="s">
         <v>162</v>
@@ -1858,112 +1858,112 @@
         <v>179</v>
       </c>
       <c r="BX1" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="BY1" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="BZ1" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="CA1" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="CB1" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="CC1" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="CD1" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="CE1" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="CF1" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="CG1" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="CH1" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="CI1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="CJ1" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="CK1" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="CL1" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="CM1" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="CN1" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="CO1" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="CP1" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="BY1" s="4" t="s">
+      <c r="CQ1" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="BZ1" s="4" t="s">
+      <c r="CR1" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="CA1" s="4" t="s">
+      <c r="CS1" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="CB1" s="4" t="s">
+      <c r="CT1" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="CC1" s="4" t="s">
+      <c r="CU1" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="CD1" s="4" t="s">
+      <c r="CV1" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="CE1" s="4" t="s">
+      <c r="CW1" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="CF1" s="4" t="s">
+      <c r="CX1" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="CG1" s="4" t="s">
+      <c r="CY1" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="CH1" s="4" t="s">
+      <c r="CZ1" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="CI1" s="4" t="s">
+      <c r="DA1" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="CJ1" s="4" t="s">
+      <c r="DB1" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="CK1" s="4" t="s">
+      <c r="DC1" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="CL1" s="4" t="s">
+      <c r="DD1" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="CM1" s="4" t="s">
+      <c r="DE1" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="CN1" s="4" t="s">
+      <c r="DF1" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="CO1" s="4" t="s">
+      <c r="DG1" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="CP1" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="CQ1" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="CR1" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="CS1" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="CT1" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="CU1" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="CV1" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="CW1" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="CX1" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="CY1" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="CZ1" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="DA1" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="DB1" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="DC1" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="DD1" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="DE1" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="DF1" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="DG1" s="4" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:111" x14ac:dyDescent="0.2">
